--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(5).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(5).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（终2）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="446">
   <si>
     <t>ID</t>
   </si>
@@ -111,7 +111,15 @@
     <t>按下去的那一瞬间，一种近乎麻木的清醒裹挟了你全身的感官，左边是克拉克惊怒的喝止，身后亚波伦带着了然的轻笑，只有时钟滴答声还在空旷的房间里清晰地回荡。</t>
   </si>
   <si>
+    <t>4 enhanced leberch-spooky-piano</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -128,7 +136,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>, 1)</t>
+      <t>, 1)&amp;unlockmusic(Music4)</t>
     </r>
   </si>
   <si>
@@ -202,6 +210,12 @@
   </si>
   <si>
     <t>“啪”</t>
+  </si>
+  <si>
+    <t>19 enhanced_suspense-tension-background-music</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music19)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=3; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"相信索菲亚","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
@@ -972,6 +986,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -1001,6 +1020,9 @@
     <t>什么不应该？</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_You; 层级=1</t>
   </si>
   <si>
@@ -1041,6 +1063,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1074,6 +1101,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2997,9 +3029,6 @@
       <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
@@ -3030,21 +3059,21 @@
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="90" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3062,27 +3091,27 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3100,7 +3129,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3115,12 +3144,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3138,7 +3167,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3153,21 +3182,21 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:12">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3176,7 +3205,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3188,15 +3217,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="54" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3205,7 +3234,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3214,7 +3243,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3226,24 +3255,24 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3252,7 +3281,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3264,15 +3293,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3281,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3290,7 +3319,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3302,15 +3331,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3328,7 +3357,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3343,21 +3372,21 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="28.5" spans="1:12">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3366,7 +3395,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3378,15 +3407,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3395,7 +3424,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3404,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3416,15 +3445,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="42" spans="1:12">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3442,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3457,21 +3486,21 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:12">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3480,7 +3509,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3492,15 +3521,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:12">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3509,7 +3538,7 @@
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3518,7 +3547,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3533,21 +3562,21 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3556,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3571,12 +3600,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="43.5" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3585,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3594,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3606,18 +3635,18 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="43.5" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3632,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3647,12 +3676,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3670,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3685,21 +3714,21 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3708,7 +3737,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3720,24 +3749,24 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3746,7 +3775,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3758,15 +3787,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3784,7 +3813,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3799,21 +3828,21 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3822,7 +3851,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3834,24 +3863,24 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="43.5" spans="1:12">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3860,7 +3889,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3875,12 +3904,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="55.5" spans="1:12">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3889,7 +3918,7 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3898,7 +3927,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3910,15 +3939,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3936,7 +3965,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3951,21 +3980,21 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3974,7 +4003,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3986,15 +4015,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4003,7 +4032,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4012,7 +4041,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -4027,21 +4056,21 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" ht="55.5" spans="1:12">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4050,7 +4079,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4065,12 +4094,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:12">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4079,7 +4108,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4088,7 +4117,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4100,24 +4129,24 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" ht="70.5" spans="1:12">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4126,7 +4155,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4138,15 +4167,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:12">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4155,7 +4184,7 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4164,7 +4193,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4176,24 +4205,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" ht="70.5" spans="1:12">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4202,7 +4231,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4214,15 +4243,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4231,7 +4260,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4240,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4252,15 +4281,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L37" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:12">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4278,7 +4307,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4293,12 +4322,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" ht="28.5" spans="1:12">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4316,7 +4345,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4331,21 +4360,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:12">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4354,7 +4383,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4366,15 +4395,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="30" spans="1:12">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4383,7 +4412,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4392,7 +4421,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4407,21 +4436,21 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" ht="55.5" spans="1:12">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4430,7 +4459,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4445,12 +4474,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4459,7 +4488,7 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4468,7 +4497,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4480,24 +4509,24 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" ht="30" spans="1:12">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4506,7 +4535,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4518,15 +4547,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4535,7 +4564,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4544,7 +4573,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4556,24 +4585,24 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4582,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4594,15 +4623,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4611,7 +4640,7 @@
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4620,7 +4649,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4635,21 +4664,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" ht="42" spans="1:12">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4658,7 +4687,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4673,12 +4702,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4687,7 +4716,7 @@
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4696,7 +4725,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4708,24 +4737,24 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4734,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4746,15 +4775,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4763,7 +4792,7 @@
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4772,7 +4801,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4784,24 +4813,24 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" ht="42" spans="1:12">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4810,7 +4839,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4822,15 +4851,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4839,7 +4868,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4848,7 +4877,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4860,15 +4889,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L53" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4886,7 +4915,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4898,15 +4927,15 @@
         <v>15</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4924,7 +4953,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4936,15 +4965,15 @@
         <v>15</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L55" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4962,7 +4991,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4982,7 +5011,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -5020,16 +5049,16 @@
     </row>
     <row r="58" ht="90" spans="1:12">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5038,7 +5067,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5050,25 +5079,25 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L58" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" ht="55.5" spans="1:12">
       <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
+        <v>195</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
         <v>196</v>
       </c>
-      <c r="B59" t="s">
-        <v>192</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>193</v>
-      </c>
       <c r="E59" t="s">
         <v>15</v>
       </c>
@@ -5076,7 +5105,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5091,21 +5120,21 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5114,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5126,15 +5155,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L60" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5152,7 +5181,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5167,21 +5196,21 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B62" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5190,7 +5219,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5202,24 +5231,24 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" ht="54" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5228,7 +5257,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5240,15 +5269,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5266,7 +5295,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5278,24 +5307,24 @@
         <v>15</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L64" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" ht="42" spans="1:12">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5304,7 +5333,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5316,15 +5345,15 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L65" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5333,7 +5362,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5342,7 +5371,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5354,24 +5383,24 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L66" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5380,7 +5409,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5392,24 +5421,24 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L67" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5418,7 +5447,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5430,15 +5459,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L68" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" ht="54" spans="1:12">
       <c r="A69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5456,7 +5485,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5471,21 +5500,21 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5494,7 +5523,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5506,15 +5535,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L70" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" ht="54" spans="1:12">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5523,7 +5552,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5532,7 +5561,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5544,21 +5573,21 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" ht="55.5" spans="1:12">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5567,7 +5596,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5582,12 +5611,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5596,7 +5625,7 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5605,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5617,18 +5646,18 @@
         <v>15</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L73" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5643,13 +5672,13 @@
         <v>15</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
@@ -5658,12 +5687,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" ht="27" spans="1:12">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5681,7 +5710,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5693,18 +5722,18 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L75" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5719,7 +5748,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5734,15 +5763,15 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -5757,7 +5786,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5772,15 +5801,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5795,7 +5824,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5807,18 +5836,18 @@
         <v>15</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="L78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B79" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -5833,7 +5862,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5845,10 +5874,10 @@
         <v>15</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L79" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5869,122 +5898,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B15" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -6006,616 +6035,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E7" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B9" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C9" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E9" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E10" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C11" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E13" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B14" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E14" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D15" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E15" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C16" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E16" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F16" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D17" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E17" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F17" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C18" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D18" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E18" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F18" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B19" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D19" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E19" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F19" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B20" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C20" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D20" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E20" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F20" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C21" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D21" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E21" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F21" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C22" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D22" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E22" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F22" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C23" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D23" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E23" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C24" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D24" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E24" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F24" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B25" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C25" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D25" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E25" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F25" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B26" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C26" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D26" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E26" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F26" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B27" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C27" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D27" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F27" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B28" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C28" t="s">
+        <v>429</v>
+      </c>
+      <c r="D28" t="s">
         <v>425</v>
       </c>
-      <c r="D28" t="s">
-        <v>421</v>
-      </c>
       <c r="E28" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F28" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B29" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C29" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D29" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E29" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F29" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B30" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C30" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D30" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E30" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F30" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B31" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C31" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D31" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
